--- a/kurallar.xlsx
+++ b/kurallar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arsla\Desktop\tahkim_proje\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{596F33DA-11E6-451C-A35D-7E632186C60F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074ED905-187A-4F9B-8F54-FBA1364C4902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14220" yWindow="165" windowWidth="14580" windowHeight="15315" xr2:uid="{B8373401-BB14-45E6-AC3F-5D0589E5F6D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Konu_Kodu</t>
   </si>
@@ -53,34 +53,16 @@
     <t>Gerekli_Alanlar</t>
   </si>
   <si>
-    <t>DK_01</t>
-  </si>
-  <si>
-    <t>Değer Kaybı</t>
-  </si>
-  <si>
-    <t>templates/deger_kaybi.docx</t>
-  </si>
-  <si>
-    <t>HB_01</t>
-  </si>
-  <si>
-    <t>Hasar Bedeli</t>
-  </si>
-  <si>
-    <t>templates/hasar_bedeli.docx</t>
-  </si>
-  <si>
-    <t>DK_HB_01</t>
-  </si>
-  <si>
-    <t>Hasar Bedeli ve Değer Kaybı</t>
-  </si>
-  <si>
-    <t>templates/dk_hb_ortak.docx</t>
-  </si>
-  <si>
-    <t>kaza_tarihi, ilk_dava_degeri_hb, islah_edilen_tutar_hb, basvuru_sahibi_beyani, basvuru_sahibi_tarafindan_talep_edilen_faiz_turu, basvuru_sahibi_tarafindan_sunulan_ek_belgeler, sigorta_sirketi_beyani, basvuru_sahibi_kusur_orani, sigorta_sirketi_kusur_orani, basvuru_sahibi_arac_plakasi, sigorta_sirketi_arac_plakasi, bilirkisi_raporunda_tespit_edilen_hasar_bedeli_kdv_haric, bilirkisi_raporunda_tespit_edilen_hasar_bedeli_kdv_dahil, sigorta_sirketi_odemesi_hb, basvuru_sahibi_ekspertiz_ucreti_talebi, basvuru_sahibi_tarafindan_sigorta_sirketine_basvuru_tarihi, uyusmazlik_hakemi_tarafindan_kabul_en_hb, tebligat_ucreti, ilk_basvuru_ucreti, islah_tamamlama_harci, bilirkisi_ucreti_hb_dk</t>
+    <t>MASTER_01</t>
+  </si>
+  <si>
+    <t>Hasar Bedeli Genel Otomasyonu</t>
+  </si>
+  <si>
+    <t>templates/master_tahkim_karari.docx</t>
+  </si>
+  <si>
+    <t>basvuru_konusu, kaza_tarihi, basvuru_sahibi_arac_plakasi, sigorta_sirketi_arac_plakasi, ilk_dava_degeri_hb, islah_edilen_tutar_hb, basvuru_sahibi_beyani, sigorta_sirketi_cevap_verdi_mi, sigorta_sirketi_beyani, basvuru_sahibi_tarafindan_talep_edilen_faiz_turu, basvuru_sahibi_tarafindan_sunulan_ek_belgeler, bilirkisi_raporu_alindi, bilirkisi_raporunda_tespit_edilen_hasar_bedeli_kdv_haric, bilirkisi_raporunda_tespit_edilen_hasar_bedeli_kdv_dahil, sigorta_sirketi_odemesi_hb, basvuru_sahibi_kusur_orani, sigorta_sirketi_kusur_orani, uyusmazlik_hakemi_tarafindan_kabul_en_hb, basvuru_sahibi_ekspertiz_ucreti_talebi, basvuru_sahibi_tarafindan_sigorta_sirketine_basvuru_tarihi, tebligat_ucreti, ilk_basvuru_ucreti, islah_tamamlama_harci, bilirkisi_ucreti_hb_dk</t>
   </si>
 </sst>
 </file>
@@ -464,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D12DE5E-F057-4936-AAD1-3533FCCFB7DC}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -498,38 +480,11 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>